--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1955</v>
+        <v>0.0596</v>
       </c>
       <c r="E2">
-        <v>-0.0482</v>
+        <v>-0.212</v>
       </c>
       <c r="G2">
-        <v>0.8612146198366766</v>
+        <v>0.06904911180773252</v>
       </c>
       <c r="H2">
-        <v>0.8612146198366766</v>
+        <v>0.06904911180773252</v>
       </c>
       <c r="I2">
-        <v>0.4320938714025213</v>
+        <v>0.2217345872518286</v>
       </c>
       <c r="J2">
-        <v>0.3963941082788405</v>
+        <v>0.1892874998301625</v>
       </c>
       <c r="K2">
-        <v>15.276</v>
+        <v>-1.769</v>
       </c>
       <c r="L2">
-        <v>0.6055656861967811</v>
+        <v>-0.07393939393939393</v>
       </c>
       <c r="M2">
-        <v>5.08942</v>
+        <v>1.6343</v>
       </c>
       <c r="N2">
-        <v>0.02260557875099937</v>
+        <v>0.01834025361912243</v>
       </c>
       <c r="O2">
-        <v>0.3331644409531291</v>
+        <v>-0.9238552854720183</v>
       </c>
       <c r="P2">
-        <v>5.08942</v>
+        <v>1.0793</v>
       </c>
       <c r="Q2">
-        <v>0.02260557875099937</v>
+        <v>0.01211199640893278</v>
       </c>
       <c r="R2">
-        <v>0.3331644409531291</v>
+        <v>-0.6101187111362353</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.3395949336107202</v>
       </c>
       <c r="U2">
-        <v>14.931</v>
+        <v>5.534</v>
       </c>
       <c r="V2">
-        <v>0.06631873500932751</v>
+        <v>0.06210301874088205</v>
       </c>
       <c r="W2">
-        <v>0.04450202893436839</v>
+        <v>0.0004221635883905013</v>
       </c>
       <c r="X2">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y2">
-        <v>-0.06341808090793276</v>
+        <v>-0.1898899820769039</v>
       </c>
       <c r="Z2">
-        <v>0.05224007322639297</v>
+        <v>0.06480561025621578</v>
       </c>
       <c r="AA2">
-        <v>0.01564832274933819</v>
+        <v>0.01190082644628099</v>
       </c>
       <c r="AB2">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AC2">
-        <v>-0.09567019209602329</v>
+        <v>-0.1827176946617525</v>
       </c>
       <c r="AD2">
-        <v>126.757</v>
+        <v>163.339</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>126.757</v>
+        <v>163.339</v>
       </c>
       <c r="AG2">
-        <v>111.826</v>
+        <v>157.805</v>
       </c>
       <c r="AH2">
-        <v>0.3602105161453493</v>
+        <v>0.6470178134989641</v>
       </c>
       <c r="AI2">
-        <v>0.2590223697143453</v>
+        <v>0.4686794315211372</v>
       </c>
       <c r="AJ2">
-        <v>0.3318613747381042</v>
+        <v>0.6391065751371929</v>
       </c>
       <c r="AK2">
-        <v>0.2357030242224452</v>
+        <v>0.4601064217508565</v>
       </c>
       <c r="AL2">
-        <v>1.324</v>
+        <v>1.416</v>
       </c>
       <c r="AM2">
-        <v>1.304</v>
+        <v>1.195</v>
       </c>
       <c r="AN2">
-        <v>14.9671744007557</v>
+        <v>35.71031919545256</v>
       </c>
       <c r="AO2">
-        <v>8.232628398791542</v>
+        <v>3.746468926553672</v>
       </c>
       <c r="AP2">
-        <v>13.20415633486835</v>
+        <v>34.50043725404461</v>
       </c>
       <c r="AQ2">
-        <v>8.358895705521475</v>
+        <v>4.439330543933055</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ceylon Guardian Investment Trust PLC (COSE:GUAR.N0000)</t>
+          <t>Galle Face Capital Partners PLC (COSE:WAPO.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,97 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.197</v>
-      </c>
-      <c r="E3">
-        <v>0.414</v>
+        <v>0.299</v>
       </c>
       <c r="G3">
-        <v>0.8580171358629131</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.8580171358629131</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8714810281517749</v>
+        <v>0.8474576271186441</v>
       </c>
       <c r="J3">
-        <v>0.8368743902222696</v>
+        <v>0.5572324123519852</v>
       </c>
       <c r="K3">
-        <v>5.65</v>
+        <v>0.049</v>
       </c>
       <c r="L3">
-        <v>0.6915544675642595</v>
+        <v>0.8305084745762713</v>
       </c>
       <c r="M3">
-        <v>0.6919999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01520879120879121</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1224778761061947</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.6919999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01520879120879121</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1224778761061947</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>6.16</v>
+        <v>0.21</v>
       </c>
       <c r="V3">
-        <v>0.1353846153846154</v>
+        <v>0.1858407079646018</v>
       </c>
       <c r="W3">
-        <v>0.05897703549060544</v>
+        <v>0.01231155778894472</v>
       </c>
       <c r="X3">
-        <v>0.1084736032972992</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y3">
-        <v>-0.04949656780669379</v>
-      </c>
-      <c r="Z3">
-        <v>0.09056645604700145</v>
-      </c>
-      <c r="AA3">
-        <v>0.07579274767892631</v>
+        <v>-0.1780005878763497</v>
       </c>
       <c r="AB3">
-        <v>0.108247843584564</v>
-      </c>
-      <c r="AC3">
-        <v>-0.03245509590563765</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AD3">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.803</v>
+        <v>-0.21</v>
       </c>
       <c r="AH3">
-        <v>0.007785070981529537</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.003651912395020305</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1461823311585258</v>
+        <v>-0.2282608695652174</v>
       </c>
       <c r="AK3">
-        <v>-0.06335360328395034</v>
+        <v>-0.1044776119402985</v>
       </c>
       <c r="AL3">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.12</v>
-      </c>
-      <c r="AN3">
-        <v>0.05007012622720897</v>
-      </c>
-      <c r="AO3">
-        <v>58.84297520661157</v>
-      </c>
-      <c r="AP3">
-        <v>-0.8138849929873773</v>
+        <v>-0.139</v>
       </c>
       <c r="AQ3">
-        <v>59.33333333333334</v>
+        <v>-0.3597122302158273</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guardian Capital Partners PLC (COSE:WAPO.N0000)</t>
+          <t>Colombo Fort Investments PLC (COSE:CFI.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.025</v>
+        <v>0.192</v>
       </c>
       <c r="E4">
-        <v>-0.0482</v>
+        <v>1.057</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -868,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.9371069182389936</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="J4">
-        <v>0.7861635220125786</v>
+        <v>0.8525480367585631</v>
       </c>
       <c r="K4">
-        <v>0.126</v>
+        <v>0.158</v>
       </c>
       <c r="L4">
-        <v>0.7924528301886793</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -901,31 +877,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.98</v>
+        <v>0.152</v>
       </c>
       <c r="V4">
-        <v>0.9149425287356323</v>
+        <v>0.09559748427672955</v>
       </c>
       <c r="W4">
-        <v>0.03028846153846154</v>
+        <v>0.02464898595943838</v>
       </c>
       <c r="X4">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y4">
-        <v>-0.0776316483038396</v>
+        <v>-0.1656631597058561</v>
       </c>
       <c r="Z4">
-        <v>0.08594594594594594</v>
+        <v>0.02839756592292089</v>
       </c>
       <c r="AA4">
-        <v>0.06756756756756756</v>
+        <v>0.02421028907630808</v>
       </c>
       <c r="AB4">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AC4">
-        <v>-0.04035254227473359</v>
+        <v>-0.1661018565889864</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -937,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-3.98</v>
+        <v>-0.152</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -946,13 +922,22 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-10.75675675675677</v>
+        <v>-0.105702364394993</v>
+      </c>
+      <c r="AK4">
+        <v>-0.02805463270579549</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.006</v>
+      </c>
+      <c r="AO4">
+        <v>28.16666666666667</v>
+      </c>
+      <c r="AQ4">
+        <v>28.16666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ceylon Investment PLC (COSE:CINV.N0000)</t>
+          <t>Ceylon Guardian Investment Trust PLC (COSE:GUAR.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,115 +957,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.194</v>
-      </c>
-      <c r="E5">
-        <v>0.326</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1.098305084745763</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.098305084745763</v>
       </c>
       <c r="I5">
-        <v>0.8862745098039215</v>
+        <v>0.7694915254237288</v>
       </c>
       <c r="J5">
-        <v>0.8622993026998033</v>
+        <v>0.7694915254237288</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>-0.582</v>
       </c>
       <c r="L5">
-        <v>1.254901960784314</v>
+        <v>-0.1972881355932203</v>
       </c>
       <c r="M5">
-        <v>0.411</v>
+        <v>0.758</v>
       </c>
       <c r="N5">
-        <v>0.01533582089552239</v>
+        <v>0.05019867549668874</v>
       </c>
       <c r="O5">
-        <v>0.1284375</v>
+        <v>-1.302405498281787</v>
       </c>
       <c r="P5">
-        <v>0.411</v>
+        <v>0.482</v>
       </c>
       <c r="Q5">
-        <v>0.01533582089552239</v>
+        <v>0.0319205298013245</v>
       </c>
       <c r="R5">
-        <v>0.1284375</v>
+        <v>-0.8281786941580757</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.3641160949868074</v>
       </c>
       <c r="U5">
-        <v>1.32</v>
+        <v>3.18</v>
       </c>
       <c r="V5">
-        <v>0.04925373134328358</v>
+        <v>0.2105960264900662</v>
       </c>
       <c r="W5">
-        <v>0.05871559633027523</v>
+        <v>-0.007167487684729064</v>
       </c>
       <c r="X5">
-        <v>0.1079201098423011</v>
+        <v>0.2021320998105737</v>
       </c>
       <c r="Y5">
-        <v>-0.04920451351202591</v>
+        <v>-0.2092995874953028</v>
       </c>
       <c r="Z5">
-        <v>0.04812228722400452</v>
+        <v>0.03912622518137326</v>
       </c>
       <c r="AA5">
-        <v>0.04149581471757876</v>
+        <v>0.03010729869888722</v>
       </c>
       <c r="AB5">
-        <v>0.1079201098423011</v>
+        <v>0.19759442996844</v>
       </c>
       <c r="AC5">
-        <v>-0.06642429512472239</v>
+        <v>-0.1674871312695527</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5">
-        <v>-1.32</v>
+        <v>-1.63</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.0930930930930931</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AJ5">
-        <v>-0.05180533751962323</v>
+        <v>-0.1210096510764662</v>
       </c>
       <c r="AK5">
-        <v>-0.02967625899280576</v>
+        <v>-0.03191697669864892</v>
       </c>
       <c r="AL5">
-        <v>0.031</v>
+        <v>0.138</v>
       </c>
       <c r="AM5">
-        <v>0.031</v>
+        <v>0.138</v>
+      </c>
+      <c r="AN5">
+        <v>0.6798245614035089</v>
       </c>
       <c r="AO5">
-        <v>72.9032258064516</v>
+        <v>16.44927536231884</v>
+      </c>
+      <c r="AP5">
+        <v>-0.7149122807017545</v>
       </c>
       <c r="AQ5">
-        <v>72.9032258064516</v>
+        <v>16.44927536231884</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shaw Wallace Investments PLC (COSE:KZOO.N0000)</t>
+          <t>Ceylon Investment PLC (COSE:CINV.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,7 +1088,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.293</v>
+        <v>-0.0189</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,100 +1097,103 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.8737864077669903</v>
+        <v>0.7840772014475272</v>
       </c>
       <c r="J6">
-        <v>0.8737864077669903</v>
+        <v>0.7840772014475272</v>
       </c>
       <c r="K6">
-        <v>2.94</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="L6">
-        <v>14.27184466019417</v>
+        <v>-0.6791314837153196</v>
       </c>
       <c r="M6">
-        <v>0.174</v>
+        <v>0.493</v>
       </c>
       <c r="N6">
-        <v>0.01581818181818182</v>
+        <v>0.05725900116144019</v>
       </c>
       <c r="O6">
-        <v>0.05918367346938775</v>
+        <v>-0.8756660746003553</v>
       </c>
       <c r="P6">
-        <v>0.174</v>
+        <v>0.214</v>
       </c>
       <c r="Q6">
-        <v>0.01581818181818182</v>
+        <v>0.0248548199767712</v>
       </c>
       <c r="R6">
-        <v>0.05918367346938775</v>
+        <v>-0.3801065719360568</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.565922920892495</v>
       </c>
       <c r="U6">
-        <v>0.03</v>
+        <v>0.406</v>
       </c>
       <c r="V6">
-        <v>0.002727272727272727</v>
+        <v>0.04715447154471546</v>
       </c>
       <c r="W6">
-        <v>0.392</v>
+        <v>-0.01229257641921397</v>
       </c>
       <c r="X6">
-        <v>0.1079201098423011</v>
+        <v>0.197654413685897</v>
       </c>
       <c r="Y6">
-        <v>0.2840798901576989</v>
+        <v>-0.2099469901051109</v>
       </c>
       <c r="Z6">
-        <v>0.02781904118838622</v>
+        <v>0.01863758992805755</v>
       </c>
       <c r="AA6">
-        <v>0.02430790006752194</v>
+        <v>0.01461330935251799</v>
       </c>
       <c r="AB6">
-        <v>0.1079201098423011</v>
+        <v>0.1951741930132165</v>
       </c>
       <c r="AC6">
-        <v>-0.08361220977477921</v>
+        <v>-0.1805608836606985</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AG6">
-        <v>-0.03</v>
+        <v>0.143</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.05994104159842779</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.02174343538357955</v>
       </c>
       <c r="AJ6">
-        <v>-0.002734731084776663</v>
+        <v>0.01633725579801211</v>
       </c>
       <c r="AK6">
-        <v>-0.003099173553719007</v>
+        <v>0.005756148613291471</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="AM6">
-        <v>-0.019</v>
+        <v>0.046</v>
+      </c>
+      <c r="AO6">
+        <v>14.1304347826087</v>
       </c>
       <c r="AQ6">
-        <v>-9.473684210526315</v>
+        <v>14.1304347826087</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colombo Fort Investments PLC (COSE:CFI.N0000)</t>
+          <t>Shaw Wallace Investments PLC (COSE:KZOO.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,7 +1213,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.06860000000000001</v>
+        <v>0.504</v>
+      </c>
+      <c r="E7">
+        <v>-0.212</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,64 +1225,67 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.826530612244898</v>
+        <v>0.7622950819672131</v>
       </c>
       <c r="J7">
-        <v>0.8157086075019206</v>
+        <v>0.6025761124121779</v>
       </c>
       <c r="K7">
-        <v>0.603</v>
+        <v>0.219</v>
       </c>
       <c r="L7">
-        <v>6.153061224489796</v>
+        <v>1.795081967213115</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.1783</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.05183139534883721</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.8141552511415526</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.1783</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.05183139534883721</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.8141552511415526</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0.001</v>
+        <v>0.213</v>
       </c>
       <c r="V7">
-        <v>0.0003194888178913738</v>
+        <v>0.06191860465116279</v>
       </c>
       <c r="W7">
-        <v>0.1194059405940594</v>
+        <v>0.02255406797116375</v>
       </c>
       <c r="X7">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y7">
-        <v>0.01148583075175826</v>
+        <v>-0.1677580776941307</v>
       </c>
       <c r="Z7">
-        <v>0.01940978411566647</v>
+        <v>0.01260330578512396</v>
       </c>
       <c r="AA7">
-        <v>0.0158327279729032</v>
+        <v>0.007594451003541911</v>
       </c>
       <c r="AB7">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AC7">
-        <v>-0.09208738186939795</v>
+        <v>-0.1827176946617525</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1300,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.001</v>
+        <v>-0.213</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1309,22 +1306,22 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.0003195909236177693</v>
+        <v>-0.06600557793616361</v>
       </c>
       <c r="AK7">
-        <v>-0.0001560305819940708</v>
+        <v>-0.0334537458771792</v>
       </c>
       <c r="AL7">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="AM7">
-        <v>0.01</v>
+        <v>-0.076</v>
       </c>
       <c r="AO7">
-        <v>8.1</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7">
-        <v>8.1</v>
+        <v>-1.223684210526316</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colombo Investment Trust PLC (COSE:CIT.N0000)</t>
+          <t>Selinsing PLC (COSE:SELI.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,25 +1341,28 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0529</v>
+        <v>-0.255</v>
+      </c>
+      <c r="E8">
+        <v>-0.537</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="I8">
-        <v>0.8181818181818181</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="J8">
-        <v>0.8181818181818181</v>
+        <v>0.59375</v>
       </c>
       <c r="K8">
-        <v>0.348</v>
+        <v>0.016</v>
       </c>
       <c r="L8">
-        <v>3.515151515151515</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1386,31 +1386,31 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.013</v>
+        <v>0.308</v>
       </c>
       <c r="V8">
-        <v>0.002789699570815451</v>
+        <v>0.02851851851851852</v>
       </c>
       <c r="W8">
-        <v>0.06641221374045801</v>
+        <v>0.0004221635883905013</v>
       </c>
       <c r="X8">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y8">
-        <v>-0.04150789610184313</v>
+        <v>-0.1898899820769039</v>
       </c>
       <c r="Z8">
-        <v>0.01890034364261168</v>
+        <v>0.0006336633663366337</v>
       </c>
       <c r="AA8">
-        <v>0.01546391752577319</v>
+        <v>0.0003762376237623762</v>
       </c>
       <c r="AB8">
-        <v>0.1079201098423011</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AC8">
-        <v>-0.09245619231652795</v>
+        <v>-0.1899359080415321</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-0.013</v>
+        <v>-0.308</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1431,22 +1431,22 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.002797503765870454</v>
+        <v>-0.02935569958063286</v>
       </c>
       <c r="AK8">
-        <v>-0.002167750541937635</v>
+        <v>-0.01003518832268995</v>
       </c>
       <c r="AL8">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.012</v>
-      </c>
-      <c r="AO8">
-        <v>6.75</v>
-      </c>
-      <c r="AQ8">
-        <v>6.75</v>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>-15.4</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lanka Ventures PLC (COSE:LVEN.N0000)</t>
+          <t>Good Hope PLC (COSE:GOOD.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,121 +1466,112 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0357</v>
+        <v>-0.498</v>
       </c>
       <c r="E9">
-        <v>-0.0166</v>
+        <v>-0.7959999999999999</v>
       </c>
       <c r="G9">
-        <v>0.539906103286385</v>
+        <v>7.8</v>
       </c>
       <c r="H9">
-        <v>0.539906103286385</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
-        <v>0.5633802816901409</v>
+        <v>0.4</v>
       </c>
       <c r="J9">
-        <v>0.4550942015730748</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="K9">
-        <v>1.51</v>
+        <v>0.004</v>
       </c>
       <c r="L9">
-        <v>0.7089201877934272</v>
+        <v>0.4</v>
       </c>
       <c r="M9">
-        <v>0.375</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.02757352941176471</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.2483443708609271</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.375</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.02757352941176471</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.2483443708609271</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>2.55</v>
+        <v>0.111</v>
       </c>
       <c r="V9">
-        <v>0.1875</v>
+        <v>0.008409090909090909</v>
       </c>
       <c r="W9">
-        <v>0.1013422818791946</v>
+        <v>0.0001129943502824859</v>
       </c>
       <c r="X9">
-        <v>0.1981740166477857</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="Y9">
-        <v>-0.09683173476859107</v>
+        <v>-0.190199151315012</v>
       </c>
       <c r="Z9">
-        <v>0.07463209530483531</v>
+        <v>0.0002827494557072978</v>
       </c>
       <c r="AA9">
-        <v>0.03396463382447965</v>
+        <v>9.047982582633529e-05</v>
       </c>
       <c r="AB9">
-        <v>0.1328488256999983</v>
+        <v>0.1903121456652944</v>
       </c>
       <c r="AC9">
-        <v>-0.09888419187551861</v>
+        <v>-0.1902216658394681</v>
       </c>
       <c r="AD9">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>14.85</v>
+        <v>-0.111</v>
       </c>
       <c r="AH9">
-        <v>0.5612903225806452</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.3849557522123893</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.5219683655536028</v>
+        <v>-0.008480403392161358</v>
       </c>
       <c r="AK9">
-        <v>0.3481828839390386</v>
+        <v>-0.003802802425571277</v>
       </c>
       <c r="AL9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>12.08333333333333</v>
-      </c>
-      <c r="AO9">
-        <v>1.043478260869565</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>10.3125</v>
-      </c>
-      <c r="AQ9">
-        <v>1.043478260869565</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="10">
@@ -1591,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Selinsing PLC (COSE:SELI.N0000)</t>
+          <t>Lanka Ventures PLC (COSE:LVEN.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1600,46 +1591,43 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.405</v>
-      </c>
-      <c r="E10">
-        <v>-0.171</v>
+        <v>0.0596</v>
       </c>
       <c r="G10">
-        <v>0.2531645569620253</v>
+        <v>1.049525816649104</v>
       </c>
       <c r="H10">
-        <v>0.2531645569620253</v>
+        <v>1.049525816649104</v>
       </c>
       <c r="I10">
-        <v>0.9620253164556962</v>
+        <v>0.3793466807165438</v>
       </c>
       <c r="J10">
-        <v>0.920963260265514</v>
+        <v>0.3793466807165438</v>
       </c>
       <c r="K10">
-        <v>0.157</v>
+        <v>-2.11</v>
       </c>
       <c r="L10">
-        <v>0.9936708860759493</v>
+        <v>-2.223393045310853</v>
       </c>
       <c r="M10">
-        <v>0.27264</v>
+        <v>0.205</v>
       </c>
       <c r="N10">
-        <v>0.01391020408163265</v>
+        <v>0.04617117117117116</v>
       </c>
       <c r="O10">
-        <v>1.73656050955414</v>
+        <v>-0.09715639810426541</v>
       </c>
       <c r="P10">
-        <v>0.27264</v>
+        <v>0.205</v>
       </c>
       <c r="Q10">
-        <v>0.01391020408163265</v>
+        <v>0.04617117117117116</v>
       </c>
       <c r="R10">
-        <v>1.73656050955414</v>
+        <v>-0.09715639810426541</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1648,67 +1636,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.025</v>
+        <v>0.678</v>
       </c>
       <c r="V10">
-        <v>0.001275510204081633</v>
+        <v>0.1527027027027027</v>
       </c>
       <c r="W10">
-        <v>0.004617647058823529</v>
+        <v>-0.137012987012987</v>
       </c>
       <c r="X10">
-        <v>0.1079201098423011</v>
+        <v>0.4273535800457903</v>
       </c>
       <c r="Y10">
-        <v>-0.1033024627834776</v>
+        <v>-0.5643665670587773</v>
       </c>
       <c r="Z10">
-        <v>0.004653354538493255</v>
+        <v>0.03137190082644628</v>
       </c>
       <c r="AA10">
-        <v>0.004285568566942075</v>
+        <v>0.01190082644628099</v>
       </c>
       <c r="AB10">
-        <v>0.1079201098423011</v>
+        <v>0.2449056942204272</v>
       </c>
       <c r="AC10">
-        <v>-0.1036345412753591</v>
+        <v>-0.2330048677741462</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AG10">
-        <v>-0.025</v>
+        <v>8.462</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.6730486008836524</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.3158258465791293</v>
       </c>
       <c r="AJ10">
-        <v>-0.001277139208173691</v>
+        <v>0.6558673073942024</v>
       </c>
       <c r="AK10">
-        <v>-0.0006600660066006601</v>
+        <v>0.2994126388790602</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>16.95732838589981</v>
+      </c>
+      <c r="AO10">
+        <v>0.2950819672131147</v>
       </c>
       <c r="AP10">
-        <v>-0.1644736842105263</v>
+        <v>15.69944341372913</v>
+      </c>
+      <c r="AQ10">
+        <v>0.2950819672131147</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Good Hope PLC (COSE:GOOD.N0000)</t>
+          <t>First Capital Holdings PLC (COSE:CFVF.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1728,103 +1722,100 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.612</v>
+        <v>0.115</v>
       </c>
       <c r="E11">
-        <v>-0.0607</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G11">
-        <v>0.1102362204724409</v>
+        <v>-0.1468085106382979</v>
       </c>
       <c r="H11">
-        <v>0.1102362204724409</v>
+        <v>-0.1468085106382979</v>
       </c>
       <c r="I11">
-        <v>0.952755905511811</v>
+        <v>0.08989361702127659</v>
       </c>
       <c r="J11">
-        <v>0.937869094488189</v>
+        <v>0.06893617021276595</v>
       </c>
       <c r="K11">
-        <v>0.126</v>
+        <v>1.04</v>
       </c>
       <c r="L11">
-        <v>0.9921259842519685</v>
+        <v>0.05531914893617021</v>
       </c>
       <c r="M11">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.01088541666666667</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>1.658730158730159</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.01088541666666667</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>1.658730158730159</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>0.033</v>
+        <v>0.276</v>
       </c>
       <c r="V11">
-        <v>0.00171875</v>
+        <v>0.008961038961038961</v>
       </c>
       <c r="W11">
-        <v>0.004038461538461539</v>
+        <v>0.04837209302325582</v>
       </c>
       <c r="X11">
-        <v>0.1079201098423011</v>
+        <v>0.7589549375589757</v>
       </c>
       <c r="Y11">
-        <v>-0.1038816483038396</v>
+        <v>-0.7105828445357198</v>
       </c>
       <c r="Z11">
-        <v>0.004079534868780315</v>
+        <v>0.1449241846087432</v>
       </c>
       <c r="AA11">
-        <v>0.003826069673315987</v>
+        <v>0.009990518258134641</v>
       </c>
       <c r="AB11">
-        <v>0.1079201098423011</v>
+        <v>0.2553648983338263</v>
       </c>
       <c r="AC11">
-        <v>-0.1040940401689852</v>
+        <v>-0.2453743800756916</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>152.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>152.1</v>
       </c>
       <c r="AG11">
-        <v>-0.033</v>
+        <v>151.824</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.8316019682886823</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.9195888754534461</v>
       </c>
       <c r="AJ11">
-        <v>-0.001721709187666302</v>
+        <v>0.8313474680217277</v>
       </c>
       <c r="AK11">
-        <v>-0.0009330732038340827</v>
+        <v>0.9194544705796855</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1833,394 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>87.91907514450867</v>
       </c>
       <c r="AP11">
-        <v>-0.2704918032786885</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Indo-Malay PLC (COSE:INDO.N0000)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.7090000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0.0111</v>
-      </c>
-      <c r="G12">
-        <v>0.04166666666666667</v>
-      </c>
-      <c r="H12">
-        <v>0.04166666666666667</v>
-      </c>
-      <c r="I12">
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="J12">
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="K12">
-        <v>0.138</v>
-      </c>
-      <c r="L12">
-        <v>1.15</v>
-      </c>
-      <c r="M12">
-        <v>0.18278</v>
-      </c>
-      <c r="N12">
-        <v>0.00687142857142857</v>
-      </c>
-      <c r="O12">
-        <v>1.324492753623188</v>
-      </c>
-      <c r="P12">
-        <v>0.18278</v>
-      </c>
-      <c r="Q12">
-        <v>0.00687142857142857</v>
-      </c>
-      <c r="R12">
-        <v>1.324492753623188</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0.022</v>
-      </c>
-      <c r="V12">
-        <v>0.0008270676691729323</v>
-      </c>
-      <c r="W12">
-        <v>0.004495114006514658</v>
-      </c>
-      <c r="X12">
-        <v>0.1079201098423011</v>
-      </c>
-      <c r="Y12">
-        <v>-0.1034249958357865</v>
-      </c>
-      <c r="Z12">
-        <v>0.00392156862745098</v>
-      </c>
-      <c r="AA12">
-        <v>0.003725490196078432</v>
-      </c>
-      <c r="AB12">
-        <v>0.1079201098423011</v>
-      </c>
-      <c r="AC12">
-        <v>-0.1041946196462227</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>-0.022</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.0008277522763187597</v>
-      </c>
-      <c r="AK12">
-        <v>-0.0006289667791183029</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>-0.1929824561403509</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Shalimar (Malay) PLC (COSE:SHAL.N0000)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.9490000000000001</v>
-      </c>
-      <c r="E13">
-        <v>-0.09519999999999999</v>
-      </c>
-      <c r="G13">
-        <v>0.05504587155963303</v>
-      </c>
-      <c r="H13">
-        <v>0.05504587155963303</v>
-      </c>
-      <c r="I13">
-        <v>0.944954128440367</v>
-      </c>
-      <c r="J13">
-        <v>0.944954128440367</v>
-      </c>
-      <c r="K13">
-        <v>0.103</v>
-      </c>
-      <c r="L13">
-        <v>0.944954128440367</v>
-      </c>
-      <c r="M13">
-        <v>0.243</v>
-      </c>
-      <c r="N13">
-        <v>0.008209459459459459</v>
-      </c>
-      <c r="O13">
-        <v>2.359223300970874</v>
-      </c>
-      <c r="P13">
-        <v>0.243</v>
-      </c>
-      <c r="Q13">
-        <v>0.008209459459459459</v>
-      </c>
-      <c r="R13">
-        <v>2.359223300970874</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.02</v>
-      </c>
-      <c r="V13">
-        <v>0.0006756756756756756</v>
-      </c>
-      <c r="W13">
-        <v>0.003399339933993399</v>
-      </c>
-      <c r="X13">
-        <v>0.1079201098423011</v>
-      </c>
-      <c r="Y13">
-        <v>-0.1045207699083077</v>
-      </c>
-      <c r="Z13">
-        <v>0.003599498051647844</v>
-      </c>
-      <c r="AA13">
-        <v>0.003401360544217687</v>
-      </c>
-      <c r="AB13">
-        <v>0.1079201098423011</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1045187492980835</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>-0.02</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.000676132521974307</v>
-      </c>
-      <c r="AK13">
-        <v>-0.0005783689994216311</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>-0.1941747572815534</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>First Capital Holdings PLC (COSE:CFVF.N0000)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>-0.0466</v>
-      </c>
-      <c r="E14">
-        <v>-0.293</v>
-      </c>
-      <c r="G14">
-        <v>1.194690265486726</v>
-      </c>
-      <c r="H14">
-        <v>1.194690265486726</v>
-      </c>
-      <c r="I14">
-        <v>-0.05849557522123894</v>
-      </c>
-      <c r="J14">
-        <v>-0.02924778761061947</v>
-      </c>
-      <c r="K14">
-        <v>0.375</v>
-      </c>
-      <c r="L14">
-        <v>0.0331858407079646</v>
-      </c>
-      <c r="M14">
-        <v>2.53</v>
-      </c>
-      <c r="N14">
-        <v>0.1199052132701422</v>
-      </c>
-      <c r="O14">
-        <v>6.746666666666666</v>
-      </c>
-      <c r="P14">
-        <v>2.53</v>
-      </c>
-      <c r="Q14">
-        <v>0.1199052132701422</v>
-      </c>
-      <c r="R14">
-        <v>6.746666666666666</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0.777</v>
-      </c>
-      <c r="V14">
-        <v>0.03682464454976303</v>
-      </c>
-      <c r="W14">
-        <v>0.01436781609195402</v>
-      </c>
-      <c r="X14">
-        <v>0.4723380197634492</v>
-      </c>
-      <c r="Y14">
-        <v>-0.4579702036714952</v>
-      </c>
-      <c r="Z14">
-        <v>0.06822147225559506</v>
-      </c>
-      <c r="AA14">
-        <v>-0.001995327131015413</v>
-      </c>
-      <c r="AB14">
-        <v>0.1431902984252094</v>
-      </c>
-      <c r="AC14">
-        <v>-0.1451856255562248</v>
-      </c>
-      <c r="AD14">
-        <v>109</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>109</v>
-      </c>
-      <c r="AG14">
-        <v>108.223</v>
-      </c>
-      <c r="AH14">
-        <v>0.8378170637970792</v>
-      </c>
-      <c r="AI14">
-        <v>0.8282674772036475</v>
-      </c>
-      <c r="AJ14">
-        <v>0.8368426343341865</v>
-      </c>
-      <c r="AK14">
-        <v>0.827247502350504</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>-184.1216216216216</v>
-      </c>
-      <c r="AP14">
-        <v>-182.8091216216216</v>
+        <v>87.75953757225433</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0596</v>
+        <v>0.0892</v>
       </c>
       <c r="E2">
-        <v>-0.212</v>
+        <v>0.15375</v>
       </c>
       <c r="G2">
-        <v>0.06904911180773252</v>
+        <v>0.1442163386662891</v>
       </c>
       <c r="H2">
-        <v>0.06904911180773252</v>
+        <v>0.1442163386662891</v>
       </c>
       <c r="I2">
-        <v>0.2217345872518286</v>
+        <v>0.557326914908679</v>
       </c>
       <c r="J2">
-        <v>0.1892874998301625</v>
+        <v>0.5202269357322434</v>
       </c>
       <c r="K2">
-        <v>-1.769</v>
+        <v>52.203</v>
       </c>
       <c r="L2">
-        <v>-0.07393939393939393</v>
+        <v>0.4927367973948747</v>
       </c>
       <c r="M2">
-        <v>1.6343</v>
+        <v>4.447</v>
       </c>
       <c r="N2">
-        <v>0.01834025361912243</v>
+        <v>0.04809127284524711</v>
       </c>
       <c r="O2">
-        <v>-0.9238552854720183</v>
+        <v>0.08518667509530105</v>
       </c>
       <c r="P2">
-        <v>1.0793</v>
+        <v>3.804</v>
       </c>
       <c r="Q2">
-        <v>0.01211199640893278</v>
+        <v>0.04113766627014167</v>
       </c>
       <c r="R2">
-        <v>-0.6101187111362353</v>
+        <v>0.07286937532325728</v>
       </c>
       <c r="S2">
-        <v>0.555</v>
+        <v>0.6429999999999999</v>
       </c>
       <c r="T2">
-        <v>0.3395949336107202</v>
+        <v>0.1445918596806836</v>
       </c>
       <c r="U2">
-        <v>5.534</v>
+        <v>7.308</v>
       </c>
       <c r="V2">
-        <v>0.06210301874088205</v>
+        <v>0.07903103709311128</v>
       </c>
       <c r="W2">
-        <v>0.0004221635883905013</v>
+        <v>0.2162528216704289</v>
       </c>
       <c r="X2">
-        <v>0.1903121456652944</v>
+        <v>0.152982224951369</v>
       </c>
       <c r="Y2">
-        <v>-0.1898899820769039</v>
+        <v>0.06327059671905988</v>
       </c>
       <c r="Z2">
-        <v>0.06480561025621578</v>
+        <v>0.3894750386001029</v>
       </c>
       <c r="AA2">
-        <v>0.01190082644628099</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="AB2">
-        <v>0.1903121456652944</v>
+        <v>0.1528359374891969</v>
       </c>
       <c r="AC2">
-        <v>-0.1827176946617525</v>
+        <v>-0.1287431967336269</v>
       </c>
       <c r="AD2">
-        <v>163.339</v>
+        <v>173.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>163.339</v>
+        <v>173.99</v>
       </c>
       <c r="AG2">
-        <v>157.805</v>
+        <v>166.682</v>
       </c>
       <c r="AH2">
-        <v>0.6470178134989641</v>
+        <v>0.6529685506267356</v>
       </c>
       <c r="AI2">
-        <v>0.4686794315211372</v>
+        <v>0.4573268497831515</v>
       </c>
       <c r="AJ2">
-        <v>0.6391065751371929</v>
+        <v>0.6431823794529851</v>
       </c>
       <c r="AK2">
-        <v>0.4601064217508565</v>
+        <v>0.44669857587728</v>
       </c>
       <c r="AL2">
-        <v>1.416</v>
+        <v>2.826</v>
       </c>
       <c r="AM2">
-        <v>1.195</v>
+        <v>2.282</v>
       </c>
       <c r="AN2">
-        <v>35.71031919545256</v>
+        <v>3.030498319196001</v>
       </c>
       <c r="AO2">
-        <v>3.746468926553672</v>
+        <v>20.89384288747346</v>
       </c>
       <c r="AP2">
-        <v>34.50043725404461</v>
+        <v>2.9032100743734</v>
       </c>
       <c r="AQ2">
-        <v>4.439330543933055</v>
+        <v>25.87467134092901</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Galle Face Capital Partners PLC (COSE:WAPO.N0000)</t>
+          <t>First Capital Holdings PLC (COSE:CFVF.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,97 +722,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.299</v>
+        <v>0.522</v>
+      </c>
+      <c r="E3">
+        <v>0.5610000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1273486430062631</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1273486430062631</v>
       </c>
       <c r="I3">
-        <v>0.8474576271186441</v>
+        <v>0.5354906054279749</v>
       </c>
       <c r="J3">
-        <v>0.5572324123519852</v>
+        <v>0.3706434974825003</v>
       </c>
       <c r="K3">
-        <v>0.049</v>
+        <v>31.7</v>
       </c>
       <c r="L3">
-        <v>0.8305084745762713</v>
+        <v>0.3308977035490606</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.82</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.08011363636363636</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.08895899053627759</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.82</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.08011363636363636</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.08895899053627759</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.21</v>
+        <v>0.295</v>
       </c>
       <c r="V3">
-        <v>0.1858407079646018</v>
+        <v>0.008380681818181817</v>
       </c>
       <c r="W3">
-        <v>0.01231155778894472</v>
+        <v>2.641666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1903121456652944</v>
+        <v>0.5484270915229694</v>
       </c>
       <c r="Y3">
-        <v>-0.1780005878763497</v>
+        <v>2.093239575143697</v>
+      </c>
+      <c r="Z3">
+        <v>0.5847739037015334</v>
+      </c>
+      <c r="AA3">
+        <v>0.2167426449044312</v>
       </c>
       <c r="AB3">
-        <v>0.1903121456652944</v>
+        <v>0.2128593610713193</v>
+      </c>
+      <c r="AC3">
+        <v>0.003883283833111872</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>162.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>162.2</v>
       </c>
       <c r="AG3">
-        <v>-0.21</v>
+        <v>161.905</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8216818642350557</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.7731172545281221</v>
       </c>
       <c r="AJ3">
-        <v>-0.2282608695652174</v>
+        <v>0.821414981862459</v>
       </c>
       <c r="AK3">
-        <v>-0.1044776119402985</v>
+        <v>0.7727977852557218</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.139</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.3597122302158273</v>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>3.161793372319688</v>
+      </c>
+      <c r="AP3">
+        <v>3.156042884990254</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Colombo Fort Investments PLC (COSE:CFI.N0000)</t>
+          <t>Ceylon Guardian Investment Trust PLC (COSE:GUAR.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,112 +850,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.192</v>
-      </c>
-      <c r="E4">
-        <v>1.057</v>
+        <v>0.144</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.3759398496240601</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.3759398496240601</v>
       </c>
       <c r="I4">
-        <v>0.9285714285714286</v>
+        <v>0.8285714285714285</v>
       </c>
       <c r="J4">
-        <v>0.8525480367585631</v>
+        <v>0.7823887587822014</v>
       </c>
       <c r="K4">
-        <v>0.158</v>
+        <v>9.58</v>
       </c>
       <c r="L4">
-        <v>0.8681318681318682</v>
+        <v>1.440601503759398</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.946</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04167400881057268</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.0987473903966597</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.624</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02748898678414097</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.06513569937369519</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.322</v>
+      </c>
+      <c r="T4">
+        <v>0.3403805496828752</v>
       </c>
       <c r="U4">
-        <v>0.152</v>
+        <v>4.71</v>
       </c>
       <c r="V4">
-        <v>0.09559748427672955</v>
+        <v>0.207488986784141</v>
       </c>
       <c r="W4">
-        <v>0.02464898595943838</v>
+        <v>0.2162528216704289</v>
       </c>
       <c r="X4">
-        <v>0.1903121456652944</v>
+        <v>0.1527948944803163</v>
       </c>
       <c r="Y4">
-        <v>-0.1656631597058561</v>
+        <v>0.06345792719011265</v>
       </c>
       <c r="Z4">
-        <v>0.02839756592292089</v>
+        <v>0.155847199437544</v>
       </c>
       <c r="AA4">
-        <v>0.02421028907630808</v>
+        <v>0.1219330969276222</v>
       </c>
       <c r="AB4">
-        <v>0.1903121456652944</v>
+        <v>0.1526779406136402</v>
       </c>
       <c r="AC4">
-        <v>-0.1661018565889864</v>
+        <v>-0.03074484368601801</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AG4">
-        <v>-0.152</v>
+        <v>-4.5</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.009166302924487123</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.002773741909919429</v>
       </c>
       <c r="AJ4">
-        <v>-0.105702364394993</v>
+        <v>-0.2472527472527473</v>
       </c>
       <c r="AK4">
-        <v>-0.02805463270579549</v>
+        <v>-0.06338028169014084</v>
       </c>
       <c r="AL4">
-        <v>0.006</v>
+        <v>0.386</v>
       </c>
       <c r="AM4">
-        <v>0.006</v>
+        <v>0.384</v>
+      </c>
+      <c r="AN4">
+        <v>0.03804347826086957</v>
       </c>
       <c r="AO4">
-        <v>28.16666666666667</v>
+        <v>14.27461139896373</v>
+      </c>
+      <c r="AP4">
+        <v>-0.8152173913043479</v>
       </c>
       <c r="AQ4">
-        <v>28.16666666666667</v>
+        <v>14.34895833333333</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ceylon Guardian Investment Trust PLC (COSE:GUAR.N0000)</t>
+          <t>Ceylon Investment PLC (COSE:CINV.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,118 +981,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.09759999999999999</v>
+        <v>0.0892</v>
       </c>
       <c r="G5">
-        <v>1.098305084745763</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1.098305084745763</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.7694915254237288</v>
+        <v>0.8342541436464088</v>
       </c>
       <c r="J5">
-        <v>0.7694915254237288</v>
+        <v>0.8030778642298648</v>
       </c>
       <c r="K5">
-        <v>-0.582</v>
+        <v>5.56</v>
       </c>
       <c r="L5">
-        <v>-0.1972881355932203</v>
+        <v>3.071823204419889</v>
       </c>
       <c r="M5">
-        <v>0.758</v>
+        <v>0.49</v>
       </c>
       <c r="N5">
-        <v>0.05019867549668874</v>
+        <v>0.035</v>
       </c>
       <c r="O5">
-        <v>-1.302405498281787</v>
+        <v>0.08812949640287771</v>
       </c>
       <c r="P5">
-        <v>0.482</v>
+        <v>0.169</v>
       </c>
       <c r="Q5">
-        <v>0.0319205298013245</v>
+        <v>0.01207142857142857</v>
       </c>
       <c r="R5">
-        <v>-0.8281786941580757</v>
+        <v>0.03039568345323741</v>
       </c>
       <c r="S5">
-        <v>0.276</v>
+        <v>0.321</v>
       </c>
       <c r="T5">
-        <v>0.3641160949868074</v>
+        <v>0.6551020408163264</v>
       </c>
       <c r="U5">
-        <v>3.18</v>
+        <v>1.66</v>
       </c>
       <c r="V5">
-        <v>0.2105960264900662</v>
+        <v>0.1185714285714286</v>
       </c>
       <c r="W5">
-        <v>-0.007167487684729064</v>
+        <v>0.2251012145748988</v>
       </c>
       <c r="X5">
-        <v>0.2021320998105737</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="Y5">
-        <v>-0.2092995874953028</v>
+        <v>0.07310220388778355</v>
       </c>
       <c r="Z5">
-        <v>0.03912622518137326</v>
+        <v>0.07285754538501792</v>
       </c>
       <c r="AA5">
-        <v>0.03010729869888722</v>
+        <v>0.05851028194083063</v>
       </c>
       <c r="AB5">
-        <v>0.19759442996844</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="AC5">
-        <v>-0.1674871312695527</v>
+        <v>-0.09348872874628461</v>
       </c>
       <c r="AD5">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-1.63</v>
+        <v>-1.66</v>
       </c>
       <c r="AH5">
-        <v>0.0930930930930931</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.02857142857142857</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1210096510764662</v>
+        <v>-0.1345218800648298</v>
       </c>
       <c r="AK5">
-        <v>-0.03191697669864892</v>
+        <v>-0.04862331575864089</v>
       </c>
       <c r="AL5">
-        <v>0.138</v>
+        <v>0.154</v>
       </c>
       <c r="AM5">
-        <v>0.138</v>
-      </c>
-      <c r="AN5">
-        <v>0.6798245614035089</v>
+        <v>0.154</v>
       </c>
       <c r="AO5">
-        <v>16.44927536231884</v>
-      </c>
-      <c r="AP5">
-        <v>-0.7149122807017545</v>
+        <v>9.805194805194805</v>
       </c>
       <c r="AQ5">
-        <v>16.44927536231884</v>
+        <v>9.805194805194805</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ceylon Investment PLC (COSE:CINV.N0000)</t>
+          <t>Galle Face Capital Partners PLC (COSE:WAPO.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,7 +1106,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0189</v>
+        <v>0.0545</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,103 +1115,103 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.7840772014475272</v>
+        <v>0.9368421052631578</v>
       </c>
       <c r="J6">
-        <v>0.7840772014475272</v>
+        <v>0.8765151515151514</v>
       </c>
       <c r="K6">
-        <v>-0.5629999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="L6">
-        <v>-0.6791314837153196</v>
+        <v>12.94736842105263</v>
       </c>
       <c r="M6">
-        <v>0.493</v>
+        <v>0.09</v>
       </c>
       <c r="N6">
-        <v>0.05725900116144019</v>
+        <v>0.04225352112676056</v>
       </c>
       <c r="O6">
-        <v>-0.8756660746003553</v>
+        <v>0.07317073170731707</v>
       </c>
       <c r="P6">
-        <v>0.214</v>
+        <v>0.09</v>
       </c>
       <c r="Q6">
-        <v>0.0248548199767712</v>
+        <v>0.04225352112676056</v>
       </c>
       <c r="R6">
-        <v>-0.3801065719360568</v>
+        <v>0.07317073170731707</v>
       </c>
       <c r="S6">
-        <v>0.279</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.565922920892495</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.406</v>
+        <v>0.019</v>
       </c>
       <c r="V6">
-        <v>0.04715447154471546</v>
+        <v>0.00892018779342723</v>
       </c>
       <c r="W6">
-        <v>-0.01229257641921397</v>
+        <v>0.5540540540540539</v>
       </c>
       <c r="X6">
-        <v>0.197654413685897</v>
+        <v>0.1540993040685025</v>
       </c>
       <c r="Y6">
-        <v>-0.2099469901051109</v>
+        <v>0.3999547499855515</v>
       </c>
       <c r="Z6">
-        <v>0.01863758992805755</v>
+        <v>0.04726368159203979</v>
       </c>
       <c r="AA6">
-        <v>0.01461330935251799</v>
+        <v>0.04142733303181063</v>
       </c>
       <c r="AB6">
-        <v>0.1951741930132165</v>
+        <v>0.1537641514493425</v>
       </c>
       <c r="AC6">
-        <v>-0.1805608836606985</v>
+        <v>-0.1123368184175319</v>
       </c>
       <c r="AD6">
-        <v>0.549</v>
+        <v>0.052</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.549</v>
+        <v>0.052</v>
       </c>
       <c r="AG6">
-        <v>0.143</v>
+        <v>0.033</v>
       </c>
       <c r="AH6">
-        <v>0.05994104159842779</v>
+        <v>0.02383134738771769</v>
       </c>
       <c r="AI6">
-        <v>0.02174343538357955</v>
+        <v>0.01371308016877637</v>
       </c>
       <c r="AJ6">
-        <v>0.01633725579801211</v>
+        <v>0.01525658807212205</v>
       </c>
       <c r="AK6">
-        <v>0.005756148613291471</v>
+        <v>0.008746355685131196</v>
       </c>
       <c r="AL6">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="AM6">
-        <v>0.046</v>
+        <v>-0.208</v>
       </c>
       <c r="AO6">
-        <v>14.1304347826087</v>
+        <v>1.412698412698413</v>
       </c>
       <c r="AQ6">
-        <v>14.1304347826087</v>
+        <v>-0.4278846153846153</v>
       </c>
     </row>
     <row r="7">
@@ -1204,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shaw Wallace Investments PLC (COSE:KZOO.N0000)</t>
+          <t>Colombo Fort Investments PLC (COSE:CFI.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,10 +1231,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.504</v>
-      </c>
-      <c r="E7">
-        <v>-0.212</v>
+        <v>0.128</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,67 +1240,64 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.7622950819672131</v>
+        <v>0.7544910179640718</v>
       </c>
       <c r="J7">
-        <v>0.6025761124121779</v>
+        <v>0.7544910179640718</v>
       </c>
       <c r="K7">
-        <v>0.219</v>
+        <v>0.193</v>
       </c>
       <c r="L7">
-        <v>1.795081967213115</v>
+        <v>1.155688622754491</v>
       </c>
       <c r="M7">
-        <v>0.1783</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05183139534883721</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.8141552511415526</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>0.1783</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05183139534883721</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.8141552511415526</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0.213</v>
+        <v>0.04</v>
       </c>
       <c r="V7">
-        <v>0.06191860465116279</v>
+        <v>0.02424242424242425</v>
       </c>
       <c r="W7">
-        <v>0.02255406797116375</v>
+        <v>0.03464991023339318</v>
       </c>
       <c r="X7">
-        <v>0.1903121456652944</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="Y7">
-        <v>-0.1677580776941307</v>
+        <v>-0.1173491004537221</v>
       </c>
       <c r="Z7">
-        <v>0.01260330578512396</v>
+        <v>0.03082318198597268</v>
       </c>
       <c r="AA7">
-        <v>0.007594451003541911</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="AB7">
-        <v>0.1903121456652944</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="AC7">
-        <v>-0.1827176946617525</v>
+        <v>-0.1287431967336269</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1297,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.213</v>
+        <v>-0.04</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1306,22 +1318,16 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.06600557793616361</v>
+        <v>-0.02484472049689441</v>
       </c>
       <c r="AK7">
-        <v>-0.0334537458771792</v>
+        <v>-0.0062402496099844</v>
       </c>
       <c r="AL7">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.076</v>
-      </c>
-      <c r="AO7">
-        <v>15.5</v>
-      </c>
-      <c r="AQ7">
-        <v>-1.223684210526316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1332,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Selinsing PLC (COSE:SELI.N0000)</t>
+          <t>Shaw Wallace Investments PLC (COSE:KZOO.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,112 +1347,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.255</v>
+        <v>0.501</v>
       </c>
       <c r="E8">
-        <v>-0.537</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G8">
-        <v>4.083333333333333</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>4.083333333333333</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.7916666666666666</v>
+        <v>0.7412587412587412</v>
       </c>
       <c r="J8">
-        <v>0.59375</v>
+        <v>0.7079217079217079</v>
       </c>
       <c r="K8">
-        <v>0.016</v>
+        <v>1.21</v>
       </c>
       <c r="L8">
-        <v>0.6666666666666666</v>
+        <v>8.461538461538462</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.101</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.0221978021978022</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.08347107438016529</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.101</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.0221978021978022</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.08347107438016529</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.308</v>
+        <v>0.02</v>
       </c>
       <c r="V8">
-        <v>0.02851851851851852</v>
+        <v>0.004395604395604396</v>
       </c>
       <c r="W8">
-        <v>0.0004221635883905013</v>
+        <v>0.2192028985507246</v>
       </c>
       <c r="X8">
-        <v>0.1903121456652944</v>
+        <v>0.152982224951369</v>
       </c>
       <c r="Y8">
-        <v>-0.1898899820769039</v>
+        <v>0.0662206735993556</v>
       </c>
       <c r="Z8">
-        <v>0.0006336633663366337</v>
+        <v>0.0278915545153111</v>
       </c>
       <c r="AA8">
-        <v>0.0003762376237623762</v>
+        <v>0.01974503690907046</v>
       </c>
       <c r="AB8">
-        <v>0.1903121456652944</v>
+        <v>0.1528359374891969</v>
       </c>
       <c r="AC8">
-        <v>-0.1899359080415321</v>
+        <v>-0.1330909005801265</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AG8">
-        <v>-0.308</v>
+        <v>0.032</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.01129943502824859</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.005763688760806916</v>
       </c>
       <c r="AJ8">
-        <v>-0.02935569958063286</v>
+        <v>0.006983849847228285</v>
       </c>
       <c r="AK8">
-        <v>-0.01003518832268995</v>
+        <v>0.003554765607642746</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>-15.4</v>
+        <v>-0.202</v>
+      </c>
+      <c r="AO8">
+        <v>1.536231884057971</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.5247524752475247</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Good Hope PLC (COSE:GOOD.N0000)</t>
+          <t>Colombo Investment Trust PLC (COSE:CIT.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,28 +1475,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.498</v>
-      </c>
-      <c r="E9">
-        <v>-0.7959999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="G9">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.4</v>
+        <v>0.8411214953271028</v>
       </c>
       <c r="J9">
-        <v>0.3200000000000001</v>
+        <v>0.8411214953271028</v>
       </c>
       <c r="K9">
-        <v>0.004</v>
+        <v>0.08</v>
       </c>
       <c r="L9">
-        <v>0.4</v>
+        <v>0.7476635514018692</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1511,31 +1517,31 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.111</v>
+        <v>0.019</v>
       </c>
       <c r="V9">
-        <v>0.008409090909090909</v>
+        <v>0.008675799086757991</v>
       </c>
       <c r="W9">
-        <v>0.0001129943502824859</v>
+        <v>0.01590457256461232</v>
       </c>
       <c r="X9">
-        <v>0.1903121456652944</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="Y9">
-        <v>-0.190199151315012</v>
+        <v>-0.1360944381225029</v>
       </c>
       <c r="Z9">
-        <v>0.0002827494557072978</v>
+        <v>0.02140428085617123</v>
       </c>
       <c r="AA9">
-        <v>9.047982582633529e-05</v>
+        <v>0.01800360072014403</v>
       </c>
       <c r="AB9">
-        <v>0.1903121456652944</v>
+        <v>0.1519990106871152</v>
       </c>
       <c r="AC9">
-        <v>-0.1902216658394681</v>
+        <v>-0.1339954099669712</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1547,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-0.111</v>
+        <v>-0.019</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1556,22 +1562,16 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.008480403392161358</v>
+        <v>-0.008751727314601566</v>
       </c>
       <c r="AK9">
-        <v>-0.003802802425571277</v>
+        <v>-0.003269660987781793</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <v>-22.2</v>
       </c>
     </row>
     <row r="10">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lanka Ventures PLC (COSE:LVEN.N0000)</t>
+          <t>Industrial Asphalts (Ceylon) PLC (COSE:ASPH.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,118 +1591,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0596</v>
+        <v>-0.104</v>
+      </c>
+      <c r="E10">
+        <v>-0.29</v>
       </c>
       <c r="G10">
-        <v>1.049525816649104</v>
+        <v>0.7124183006535948</v>
       </c>
       <c r="H10">
-        <v>1.049525816649104</v>
+        <v>0.7124183006535948</v>
       </c>
       <c r="I10">
-        <v>0.3793466807165438</v>
+        <v>0.3006535947712418</v>
       </c>
       <c r="J10">
-        <v>0.3793466807165438</v>
+        <v>0.2789569436021831</v>
       </c>
       <c r="K10">
-        <v>-2.11</v>
+        <v>0.27</v>
       </c>
       <c r="L10">
-        <v>-2.223393045310853</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="M10">
-        <v>0.205</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04617117117117116</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0.09715639810426541</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>0.205</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04617117117117116</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0.09715639810426541</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>0.678</v>
+        <v>0.001</v>
       </c>
       <c r="V10">
-        <v>0.1527027027027027</v>
+        <v>0.0002155172413793104</v>
       </c>
       <c r="W10">
-        <v>-0.137012987012987</v>
+        <v>0.07627118644067797</v>
       </c>
       <c r="X10">
-        <v>0.4273535800457903</v>
+        <v>0.1552622649262335</v>
       </c>
       <c r="Y10">
-        <v>-0.5643665670587773</v>
+        <v>-0.07899107848555549</v>
       </c>
       <c r="Z10">
-        <v>0.03137190082644628</v>
+        <v>0.04289318755256518</v>
       </c>
       <c r="AA10">
-        <v>0.01190082644628099</v>
+        <v>0.01196535250101879</v>
       </c>
       <c r="AB10">
-        <v>0.2449056942204272</v>
+        <v>0.1557523430519874</v>
       </c>
       <c r="AC10">
-        <v>-0.2330048677741462</v>
+        <v>-0.1437869905509686</v>
       </c>
       <c r="AD10">
-        <v>9.140000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>9.140000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="AG10">
-        <v>8.462</v>
+        <v>0.175</v>
       </c>
       <c r="AH10">
-        <v>0.6730486008836524</v>
+        <v>0.03654485049833887</v>
       </c>
       <c r="AI10">
-        <v>0.3158258465791293</v>
+        <v>0.03958614484930274</v>
       </c>
       <c r="AJ10">
-        <v>0.6558673073942024</v>
+        <v>0.03634475597092419</v>
       </c>
       <c r="AK10">
-        <v>0.2994126388790602</v>
+        <v>0.03937007874015748</v>
       </c>
       <c r="AL10">
-        <v>1.22</v>
+        <v>0.014</v>
       </c>
       <c r="AM10">
-        <v>1.22</v>
+        <v>0.014</v>
       </c>
       <c r="AN10">
-        <v>16.95732838589981</v>
+        <v>2.588235294117647</v>
       </c>
       <c r="AO10">
-        <v>0.2950819672131147</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AP10">
-        <v>15.69944341372913</v>
+        <v>2.573529411764706</v>
       </c>
       <c r="AQ10">
-        <v>0.2950819672131147</v>
+        <v>3.285714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First Capital Holdings PLC (COSE:CFVF.N0000)</t>
+          <t>Lanka Ventures PLC (COSE:LVEN.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,28 +1722,28 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.115</v>
+        <v>-0.048</v>
       </c>
       <c r="E11">
-        <v>-0.06419999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="G11">
-        <v>-0.1468085106382979</v>
+        <v>0.4607843137254902</v>
       </c>
       <c r="H11">
-        <v>-0.1468085106382979</v>
+        <v>0.4607843137254902</v>
       </c>
       <c r="I11">
-        <v>0.08989361702127659</v>
+        <v>0.2637254901960784</v>
       </c>
       <c r="J11">
-        <v>0.06893617021276595</v>
+        <v>0.2593408121194688</v>
       </c>
       <c r="K11">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="L11">
-        <v>0.05531914893617021</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1767,67 +1767,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.276</v>
+        <v>0.544</v>
       </c>
       <c r="V11">
-        <v>0.008961038961038961</v>
+        <v>0.100554528650647</v>
       </c>
       <c r="W11">
-        <v>0.04837209302325582</v>
+        <v>0.2144144144144144</v>
       </c>
       <c r="X11">
-        <v>0.7589549375589757</v>
+        <v>0.3316945936410793</v>
       </c>
       <c r="Y11">
-        <v>-0.7105828445357198</v>
+        <v>-0.1172801792266649</v>
       </c>
       <c r="Z11">
-        <v>0.1449241846087432</v>
+        <v>0.05214190778039055</v>
       </c>
       <c r="AA11">
-        <v>0.009990518258134641</v>
+        <v>0.01352252470922493</v>
       </c>
       <c r="AB11">
-        <v>0.2553648983338263</v>
+        <v>0.2020869010774075</v>
       </c>
       <c r="AC11">
-        <v>-0.2453743800756916</v>
+        <v>-0.1885643763681826</v>
       </c>
       <c r="AD11">
-        <v>152.1</v>
+        <v>11.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>152.1</v>
+        <v>11.3</v>
       </c>
       <c r="AG11">
-        <v>151.824</v>
+        <v>10.756</v>
       </c>
       <c r="AH11">
-        <v>0.8316019682886823</v>
+        <v>0.6762417713943746</v>
       </c>
       <c r="AI11">
-        <v>0.9195888754534461</v>
+        <v>0.3817567567567567</v>
       </c>
       <c r="AJ11">
-        <v>0.8313474680217277</v>
+        <v>0.665347024619572</v>
       </c>
       <c r="AK11">
-        <v>0.9194544705796855</v>
+        <v>0.370181718061674</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AN11">
-        <v>87.91907514450867</v>
+        <v>21.52380952380953</v>
+      </c>
+      <c r="AO11">
+        <v>0.1257009345794393</v>
       </c>
       <c r="AP11">
-        <v>87.75953757225433</v>
+        <v>20.48761904761905</v>
+      </c>
+      <c r="AQ11">
+        <v>0.1257009345794393</v>
       </c>
     </row>
   </sheetData>
